--- a/files/temp_files/statement_2026_12.xlsx
+++ b/files/temp_files/statement_2026_12.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>37.61</v>
+        <v>-37.61</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>610.37</v>
+        <v>-610.37</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>550.4400000000001</v>
+        <v>-550.4400000000001</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -653,7 +653,7 @@
         <v>39</v>
       </c>
       <c r="C6">
-        <v>69.87</v>
+        <v>-69.87</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
@@ -667,7 +667,7 @@
         <v>36</v>
       </c>
       <c r="C7">
-        <v>897.0700000000001</v>
+        <v>-897.0700000000001</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
@@ -681,7 +681,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>141.07</v>
+        <v>-141.07</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C9">
-        <v>88.28</v>
+        <v>-88.28</v>
       </c>
       <c r="D9" t="s">
         <v>62</v>
@@ -709,7 +709,7 @@
         <v>42</v>
       </c>
       <c r="C10">
-        <v>154.93</v>
+        <v>-154.93</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -723,7 +723,7 @@
         <v>43</v>
       </c>
       <c r="C11">
-        <v>32.71</v>
+        <v>-32.71</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -737,7 +737,7 @@
         <v>44</v>
       </c>
       <c r="C12">
-        <v>61.35</v>
+        <v>-61.35</v>
       </c>
       <c r="D12" t="s">
         <v>66</v>
@@ -751,7 +751,7 @@
         <v>45</v>
       </c>
       <c r="C13">
-        <v>306.09</v>
+        <v>-306.09</v>
       </c>
       <c r="D13" t="s">
         <v>62</v>
@@ -765,7 +765,7 @@
         <v>43</v>
       </c>
       <c r="C14">
-        <v>30.1</v>
+        <v>-30.1</v>
       </c>
       <c r="D14" t="s">
         <v>65</v>
@@ -779,7 +779,7 @@
         <v>46</v>
       </c>
       <c r="C15">
-        <v>42.03</v>
+        <v>-42.03</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -807,7 +807,7 @@
         <v>36</v>
       </c>
       <c r="C17">
-        <v>611.02</v>
+        <v>-611.02</v>
       </c>
       <c r="D17" t="s">
         <v>60</v>
@@ -821,7 +821,7 @@
         <v>47</v>
       </c>
       <c r="C18">
-        <v>13.54</v>
+        <v>-13.54</v>
       </c>
       <c r="D18" t="s">
         <v>66</v>
@@ -835,7 +835,7 @@
         <v>46</v>
       </c>
       <c r="C19">
-        <v>70.72</v>
+        <v>-70.72</v>
       </c>
       <c r="D19" t="s">
         <v>59</v>
@@ -849,7 +849,7 @@
         <v>46</v>
       </c>
       <c r="C20">
-        <v>33.7</v>
+        <v>-33.7</v>
       </c>
       <c r="D20" t="s">
         <v>59</v>
@@ -877,7 +877,7 @@
         <v>46</v>
       </c>
       <c r="C22">
-        <v>43.81</v>
+        <v>-43.81</v>
       </c>
       <c r="D22" t="s">
         <v>59</v>
@@ -905,7 +905,7 @@
         <v>36</v>
       </c>
       <c r="C24">
-        <v>681.4400000000001</v>
+        <v>-681.4400000000001</v>
       </c>
       <c r="D24" t="s">
         <v>60</v>
@@ -919,7 +919,7 @@
         <v>45</v>
       </c>
       <c r="C25">
-        <v>204.52</v>
+        <v>-204.52</v>
       </c>
       <c r="D25" t="s">
         <v>62</v>
@@ -933,7 +933,7 @@
         <v>37</v>
       </c>
       <c r="C26">
-        <v>487.26</v>
+        <v>-487.26</v>
       </c>
       <c r="D26" t="s">
         <v>60</v>
@@ -947,7 +947,7 @@
         <v>42</v>
       </c>
       <c r="C27">
-        <v>71.62</v>
+        <v>-71.62</v>
       </c>
       <c r="D27" t="s">
         <v>64</v>
@@ -961,7 +961,7 @@
         <v>46</v>
       </c>
       <c r="C28">
-        <v>10.75</v>
+        <v>-10.75</v>
       </c>
       <c r="D28" t="s">
         <v>59</v>
@@ -975,7 +975,7 @@
         <v>49</v>
       </c>
       <c r="C29">
-        <v>38.61</v>
+        <v>-38.61</v>
       </c>
       <c r="D29" t="s">
         <v>64</v>
@@ -989,7 +989,7 @@
         <v>40</v>
       </c>
       <c r="C30">
-        <v>70.83</v>
+        <v>-70.83</v>
       </c>
       <c r="D30" t="s">
         <v>63</v>
@@ -1003,7 +1003,7 @@
         <v>41</v>
       </c>
       <c r="C31">
-        <v>154.16</v>
+        <v>-154.16</v>
       </c>
       <c r="D31" t="s">
         <v>62</v>
@@ -1017,7 +1017,7 @@
         <v>37</v>
       </c>
       <c r="C32">
-        <v>223.49</v>
+        <v>-223.49</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1031,7 +1031,7 @@
         <v>50</v>
       </c>
       <c r="C33">
-        <v>47.37</v>
+        <v>-47.37</v>
       </c>
       <c r="D33" t="s">
         <v>65</v>
@@ -1045,7 +1045,7 @@
         <v>41</v>
       </c>
       <c r="C34">
-        <v>140.4</v>
+        <v>-140.4</v>
       </c>
       <c r="D34" t="s">
         <v>62</v>
@@ -1073,7 +1073,7 @@
         <v>46</v>
       </c>
       <c r="C36">
-        <v>34.23</v>
+        <v>-34.23</v>
       </c>
       <c r="D36" t="s">
         <v>59</v>
@@ -1087,7 +1087,7 @@
         <v>51</v>
       </c>
       <c r="C37">
-        <v>69.67</v>
+        <v>-69.67</v>
       </c>
       <c r="D37" t="s">
         <v>63</v>
@@ -1101,7 +1101,7 @@
         <v>44</v>
       </c>
       <c r="C38">
-        <v>146.4</v>
+        <v>-146.4</v>
       </c>
       <c r="D38" t="s">
         <v>66</v>
@@ -1129,7 +1129,7 @@
         <v>52</v>
       </c>
       <c r="C40">
-        <v>156.82</v>
+        <v>-156.82</v>
       </c>
       <c r="D40" t="s">
         <v>64</v>
@@ -1143,7 +1143,7 @@
         <v>51</v>
       </c>
       <c r="C41">
-        <v>72.64</v>
+        <v>-72.64</v>
       </c>
       <c r="D41" t="s">
         <v>63</v>
@@ -1157,7 +1157,7 @@
         <v>45</v>
       </c>
       <c r="C42">
-        <v>269.59</v>
+        <v>-269.59</v>
       </c>
       <c r="D42" t="s">
         <v>62</v>
@@ -1171,7 +1171,7 @@
         <v>44</v>
       </c>
       <c r="C43">
-        <v>13.35</v>
+        <v>-13.35</v>
       </c>
       <c r="D43" t="s">
         <v>66</v>
@@ -1213,7 +1213,7 @@
         <v>44</v>
       </c>
       <c r="C46">
-        <v>178.68</v>
+        <v>-178.68</v>
       </c>
       <c r="D46" t="s">
         <v>66</v>
@@ -1227,7 +1227,7 @@
         <v>42</v>
       </c>
       <c r="C47">
-        <v>171.09</v>
+        <v>-171.09</v>
       </c>
       <c r="D47" t="s">
         <v>64</v>
@@ -1241,7 +1241,7 @@
         <v>49</v>
       </c>
       <c r="C48">
-        <v>229.81</v>
+        <v>-229.81</v>
       </c>
       <c r="D48" t="s">
         <v>64</v>
@@ -1255,7 +1255,7 @@
         <v>54</v>
       </c>
       <c r="C49">
-        <v>55.32</v>
+        <v>-55.32</v>
       </c>
       <c r="D49" t="s">
         <v>66</v>
@@ -1269,7 +1269,7 @@
         <v>46</v>
       </c>
       <c r="C50">
-        <v>85.67</v>
+        <v>-85.67</v>
       </c>
       <c r="D50" t="s">
         <v>59</v>
@@ -1283,7 +1283,7 @@
         <v>55</v>
       </c>
       <c r="C51">
-        <v>399.54</v>
+        <v>-399.54</v>
       </c>
       <c r="D51" t="s">
         <v>60</v>
@@ -1311,7 +1311,7 @@
         <v>39</v>
       </c>
       <c r="C53">
-        <v>283.69</v>
+        <v>-283.69</v>
       </c>
       <c r="D53" t="s">
         <v>62</v>
@@ -1325,7 +1325,7 @@
         <v>56</v>
       </c>
       <c r="C54">
-        <v>79.73</v>
+        <v>-79.73</v>
       </c>
       <c r="D54" t="s">
         <v>59</v>
@@ -1339,7 +1339,7 @@
         <v>44</v>
       </c>
       <c r="C55">
-        <v>186.44</v>
+        <v>-186.44</v>
       </c>
       <c r="D55" t="s">
         <v>66</v>
@@ -1367,7 +1367,7 @@
         <v>36</v>
       </c>
       <c r="C57">
-        <v>126.97</v>
+        <v>-126.97</v>
       </c>
       <c r="D57" t="s">
         <v>60</v>
@@ -1381,7 +1381,7 @@
         <v>54</v>
       </c>
       <c r="C58">
-        <v>150.47</v>
+        <v>-150.47</v>
       </c>
       <c r="D58" t="s">
         <v>66</v>
@@ -1395,7 +1395,7 @@
         <v>51</v>
       </c>
       <c r="C59">
-        <v>64.17</v>
+        <v>-64.17</v>
       </c>
       <c r="D59" t="s">
         <v>63</v>
@@ -1409,7 +1409,7 @@
         <v>47</v>
       </c>
       <c r="C60">
-        <v>15.48</v>
+        <v>-15.48</v>
       </c>
       <c r="D60" t="s">
         <v>66</v>
@@ -1423,7 +1423,7 @@
         <v>47</v>
       </c>
       <c r="C61">
-        <v>121.93</v>
+        <v>-121.93</v>
       </c>
       <c r="D61" t="s">
         <v>66</v>
@@ -1437,7 +1437,7 @@
         <v>47</v>
       </c>
       <c r="C62">
-        <v>107.35</v>
+        <v>-107.35</v>
       </c>
       <c r="D62" t="s">
         <v>66</v>
@@ -1465,7 +1465,7 @@
         <v>40</v>
       </c>
       <c r="C64">
-        <v>87.26000000000001</v>
+        <v>-87.26000000000001</v>
       </c>
       <c r="D64" t="s">
         <v>63</v>
@@ -1479,7 +1479,7 @@
         <v>56</v>
       </c>
       <c r="C65">
-        <v>99.31</v>
+        <v>-99.31</v>
       </c>
       <c r="D65" t="s">
         <v>59</v>
@@ -1493,7 +1493,7 @@
         <v>35</v>
       </c>
       <c r="C66">
-        <v>66.58</v>
+        <v>-66.58</v>
       </c>
       <c r="D66" t="s">
         <v>59</v>
@@ -1507,7 +1507,7 @@
         <v>46</v>
       </c>
       <c r="C67">
-        <v>92.52</v>
+        <v>-92.52</v>
       </c>
       <c r="D67" t="s">
         <v>59</v>
@@ -1521,7 +1521,7 @@
         <v>50</v>
       </c>
       <c r="C68">
-        <v>37.58</v>
+        <v>-37.58</v>
       </c>
       <c r="D68" t="s">
         <v>65</v>
@@ -1535,7 +1535,7 @@
         <v>54</v>
       </c>
       <c r="C69">
-        <v>76.47</v>
+        <v>-76.47</v>
       </c>
       <c r="D69" t="s">
         <v>66</v>
@@ -1549,7 +1549,7 @@
         <v>55</v>
       </c>
       <c r="C70">
-        <v>793.6</v>
+        <v>-793.6</v>
       </c>
       <c r="D70" t="s">
         <v>60</v>
@@ -1577,7 +1577,7 @@
         <v>55</v>
       </c>
       <c r="C72">
-        <v>567</v>
+        <v>-567</v>
       </c>
       <c r="D72" t="s">
         <v>60</v>
@@ -1605,7 +1605,7 @@
         <v>40</v>
       </c>
       <c r="C74">
-        <v>46.81</v>
+        <v>-46.81</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
@@ -1633,7 +1633,7 @@
         <v>45</v>
       </c>
       <c r="C76">
-        <v>137.94</v>
+        <v>-137.94</v>
       </c>
       <c r="D76" t="s">
         <v>62</v>
@@ -1647,7 +1647,7 @@
         <v>46</v>
       </c>
       <c r="C77">
-        <v>91.13</v>
+        <v>-91.13</v>
       </c>
       <c r="D77" t="s">
         <v>59</v>
@@ -1661,7 +1661,7 @@
         <v>49</v>
       </c>
       <c r="C78">
-        <v>284.79</v>
+        <v>-284.79</v>
       </c>
       <c r="D78" t="s">
         <v>64</v>
@@ -1675,7 +1675,7 @@
         <v>45</v>
       </c>
       <c r="C79">
-        <v>345.19</v>
+        <v>-345.19</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
@@ -1689,7 +1689,7 @@
         <v>37</v>
       </c>
       <c r="C80">
-        <v>254.58</v>
+        <v>-254.58</v>
       </c>
       <c r="D80" t="s">
         <v>60</v>
@@ -1703,7 +1703,7 @@
         <v>40</v>
       </c>
       <c r="C81">
-        <v>142.69</v>
+        <v>-142.69</v>
       </c>
       <c r="D81" t="s">
         <v>63</v>
@@ -1717,7 +1717,7 @@
         <v>54</v>
       </c>
       <c r="C82">
-        <v>81.40000000000001</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="D82" t="s">
         <v>66</v>
@@ -1731,7 +1731,7 @@
         <v>57</v>
       </c>
       <c r="C83">
-        <v>33.8</v>
+        <v>-33.8</v>
       </c>
       <c r="D83" t="s">
         <v>63</v>
@@ -1745,7 +1745,7 @@
         <v>47</v>
       </c>
       <c r="C84">
-        <v>118.86</v>
+        <v>-118.86</v>
       </c>
       <c r="D84" t="s">
         <v>66</v>
@@ -1759,7 +1759,7 @@
         <v>40</v>
       </c>
       <c r="C85">
-        <v>52.2</v>
+        <v>-52.2</v>
       </c>
       <c r="D85" t="s">
         <v>63</v>
@@ -1773,7 +1773,7 @@
         <v>35</v>
       </c>
       <c r="C86">
-        <v>48.34</v>
+        <v>-48.34</v>
       </c>
       <c r="D86" t="s">
         <v>59</v>
@@ -1787,7 +1787,7 @@
         <v>47</v>
       </c>
       <c r="C87">
-        <v>192.36</v>
+        <v>-192.36</v>
       </c>
       <c r="D87" t="s">
         <v>66</v>
@@ -1801,7 +1801,7 @@
         <v>51</v>
       </c>
       <c r="C88">
-        <v>57.53</v>
+        <v>-57.53</v>
       </c>
       <c r="D88" t="s">
         <v>63</v>
@@ -1815,7 +1815,7 @@
         <v>46</v>
       </c>
       <c r="C89">
-        <v>11.36</v>
+        <v>-11.36</v>
       </c>
       <c r="D89" t="s">
         <v>59</v>
@@ -1829,7 +1829,7 @@
         <v>49</v>
       </c>
       <c r="C90">
-        <v>202.24</v>
+        <v>-202.24</v>
       </c>
       <c r="D90" t="s">
         <v>64</v>
@@ -1843,7 +1843,7 @@
         <v>42</v>
       </c>
       <c r="C91">
-        <v>284.06</v>
+        <v>-284.06</v>
       </c>
       <c r="D91" t="s">
         <v>64</v>
@@ -1857,7 +1857,7 @@
         <v>52</v>
       </c>
       <c r="C92">
-        <v>71.66</v>
+        <v>-71.66</v>
       </c>
       <c r="D92" t="s">
         <v>64</v>
@@ -1871,7 +1871,7 @@
         <v>50</v>
       </c>
       <c r="C93">
-        <v>21.62</v>
+        <v>-21.62</v>
       </c>
       <c r="D93" t="s">
         <v>65</v>
@@ -1885,7 +1885,7 @@
         <v>46</v>
       </c>
       <c r="C94">
-        <v>57.54</v>
+        <v>-57.54</v>
       </c>
       <c r="D94" t="s">
         <v>59</v>
@@ -1899,7 +1899,7 @@
         <v>36</v>
       </c>
       <c r="C95">
-        <v>801.6799999999999</v>
+        <v>-801.6799999999999</v>
       </c>
       <c r="D95" t="s">
         <v>60</v>
@@ -1927,7 +1927,7 @@
         <v>50</v>
       </c>
       <c r="C97">
-        <v>38.17</v>
+        <v>-38.17</v>
       </c>
       <c r="D97" t="s">
         <v>65</v>
@@ -1941,7 +1941,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>189.63</v>
+        <v>-189.63</v>
       </c>
       <c r="D98" t="s">
         <v>66</v>
@@ -1955,7 +1955,7 @@
         <v>43</v>
       </c>
       <c r="C99">
-        <v>1.18</v>
+        <v>-1.18</v>
       </c>
       <c r="D99" t="s">
         <v>65</v>
@@ -1969,7 +1969,7 @@
         <v>52</v>
       </c>
       <c r="C100">
-        <v>64.25</v>
+        <v>-64.25</v>
       </c>
       <c r="D100" t="s">
         <v>64</v>
@@ -1983,7 +1983,7 @@
         <v>40</v>
       </c>
       <c r="C101">
-        <v>34.89</v>
+        <v>-34.89</v>
       </c>
       <c r="D101" t="s">
         <v>63</v>
@@ -1997,7 +1997,7 @@
         <v>43</v>
       </c>
       <c r="C102">
-        <v>32.86</v>
+        <v>-32.86</v>
       </c>
       <c r="D102" t="s">
         <v>65</v>
@@ -2011,7 +2011,7 @@
         <v>49</v>
       </c>
       <c r="C103">
-        <v>265.52</v>
+        <v>-265.52</v>
       </c>
       <c r="D103" t="s">
         <v>64</v>
@@ -2025,7 +2025,7 @@
         <v>41</v>
       </c>
       <c r="C104">
-        <v>265.04</v>
+        <v>-265.04</v>
       </c>
       <c r="D104" t="s">
         <v>62</v>
@@ -2039,7 +2039,7 @@
         <v>57</v>
       </c>
       <c r="C105">
-        <v>68.63</v>
+        <v>-68.63</v>
       </c>
       <c r="D105" t="s">
         <v>63</v>
@@ -2053,7 +2053,7 @@
         <v>51</v>
       </c>
       <c r="C106">
-        <v>86.34</v>
+        <v>-86.34</v>
       </c>
       <c r="D106" t="s">
         <v>63</v>
@@ -2067,7 +2067,7 @@
         <v>56</v>
       </c>
       <c r="C107">
-        <v>42.62</v>
+        <v>-42.62</v>
       </c>
       <c r="D107" t="s">
         <v>59</v>
@@ -2081,7 +2081,7 @@
         <v>35</v>
       </c>
       <c r="C108">
-        <v>97.39</v>
+        <v>-97.39</v>
       </c>
       <c r="D108" t="s">
         <v>59</v>
@@ -2095,7 +2095,7 @@
         <v>57</v>
       </c>
       <c r="C109">
-        <v>134.63</v>
+        <v>-134.63</v>
       </c>
       <c r="D109" t="s">
         <v>63</v>
@@ -2109,7 +2109,7 @@
         <v>40</v>
       </c>
       <c r="C110">
-        <v>70.64</v>
+        <v>-70.64</v>
       </c>
       <c r="D110" t="s">
         <v>63</v>
@@ -2123,7 +2123,7 @@
         <v>55</v>
       </c>
       <c r="C111">
-        <v>760.21</v>
+        <v>-760.21</v>
       </c>
       <c r="D111" t="s">
         <v>60</v>
@@ -2137,7 +2137,7 @@
         <v>36</v>
       </c>
       <c r="C112">
-        <v>6.47</v>
+        <v>-6.47</v>
       </c>
       <c r="D112" t="s">
         <v>60</v>
@@ -2151,7 +2151,7 @@
         <v>47</v>
       </c>
       <c r="C113">
-        <v>194.12</v>
+        <v>-194.12</v>
       </c>
       <c r="D113" t="s">
         <v>66</v>
@@ -2165,7 +2165,7 @@
         <v>49</v>
       </c>
       <c r="C114">
-        <v>233.15</v>
+        <v>-233.15</v>
       </c>
       <c r="D114" t="s">
         <v>64</v>
@@ -2179,7 +2179,7 @@
         <v>45</v>
       </c>
       <c r="C115">
-        <v>322.27</v>
+        <v>-322.27</v>
       </c>
       <c r="D115" t="s">
         <v>62</v>
@@ -2193,7 +2193,7 @@
         <v>54</v>
       </c>
       <c r="C116">
-        <v>48.81</v>
+        <v>-48.81</v>
       </c>
       <c r="D116" t="s">
         <v>66</v>
@@ -2207,7 +2207,7 @@
         <v>57</v>
       </c>
       <c r="C117">
-        <v>82.75</v>
+        <v>-82.75</v>
       </c>
       <c r="D117" t="s">
         <v>63</v>
@@ -2221,7 +2221,7 @@
         <v>41</v>
       </c>
       <c r="C118">
-        <v>307.35</v>
+        <v>-307.35</v>
       </c>
       <c r="D118" t="s">
         <v>62</v>
@@ -2235,7 +2235,7 @@
         <v>46</v>
       </c>
       <c r="C119">
-        <v>78.31</v>
+        <v>-78.31</v>
       </c>
       <c r="D119" t="s">
         <v>59</v>
@@ -2249,7 +2249,7 @@
         <v>36</v>
       </c>
       <c r="C120">
-        <v>739.17</v>
+        <v>-739.17</v>
       </c>
       <c r="D120" t="s">
         <v>60</v>
@@ -2263,7 +2263,7 @@
         <v>39</v>
       </c>
       <c r="C121">
-        <v>300.44</v>
+        <v>-300.44</v>
       </c>
       <c r="D121" t="s">
         <v>62</v>
@@ -2277,7 +2277,7 @@
         <v>46</v>
       </c>
       <c r="C122">
-        <v>81.56999999999999</v>
+        <v>-81.56999999999999</v>
       </c>
       <c r="D122" t="s">
         <v>59</v>
@@ -2291,7 +2291,7 @@
         <v>54</v>
       </c>
       <c r="C123">
-        <v>144.23</v>
+        <v>-144.23</v>
       </c>
       <c r="D123" t="s">
         <v>66</v>
@@ -2305,7 +2305,7 @@
         <v>56</v>
       </c>
       <c r="C124">
-        <v>28.25</v>
+        <v>-28.25</v>
       </c>
       <c r="D124" t="s">
         <v>59</v>
@@ -2319,7 +2319,7 @@
         <v>58</v>
       </c>
       <c r="C125">
-        <v>40.59</v>
+        <v>-40.59</v>
       </c>
       <c r="D125" t="s">
         <v>65</v>
@@ -2333,7 +2333,7 @@
         <v>52</v>
       </c>
       <c r="C126">
-        <v>254.03</v>
+        <v>-254.03</v>
       </c>
       <c r="D126" t="s">
         <v>64</v>
@@ -2347,7 +2347,7 @@
         <v>57</v>
       </c>
       <c r="C127">
-        <v>105.44</v>
+        <v>-105.44</v>
       </c>
       <c r="D127" t="s">
         <v>63</v>
@@ -2361,7 +2361,7 @@
         <v>54</v>
       </c>
       <c r="C128">
-        <v>70.98</v>
+        <v>-70.98</v>
       </c>
       <c r="D128" t="s">
         <v>66</v>
@@ -2389,7 +2389,7 @@
         <v>54</v>
       </c>
       <c r="C130">
-        <v>19.98</v>
+        <v>-19.98</v>
       </c>
       <c r="D130" t="s">
         <v>66</v>
@@ -2403,7 +2403,7 @@
         <v>47</v>
       </c>
       <c r="C131">
-        <v>118.26</v>
+        <v>-118.26</v>
       </c>
       <c r="D131" t="s">
         <v>66</v>
@@ -2417,7 +2417,7 @@
         <v>45</v>
       </c>
       <c r="C132">
-        <v>434.63</v>
+        <v>-434.63</v>
       </c>
       <c r="D132" t="s">
         <v>62</v>
@@ -2431,7 +2431,7 @@
         <v>52</v>
       </c>
       <c r="C133">
-        <v>166.74</v>
+        <v>-166.74</v>
       </c>
       <c r="D133" t="s">
         <v>64</v>
@@ -2459,7 +2459,7 @@
         <v>58</v>
       </c>
       <c r="C135">
-        <v>45</v>
+        <v>-45</v>
       </c>
       <c r="D135" t="s">
         <v>65</v>
@@ -2473,7 +2473,7 @@
         <v>37</v>
       </c>
       <c r="C136">
-        <v>772.55</v>
+        <v>-772.55</v>
       </c>
       <c r="D136" t="s">
         <v>60</v>
@@ -2487,7 +2487,7 @@
         <v>56</v>
       </c>
       <c r="C137">
-        <v>21.17</v>
+        <v>-21.17</v>
       </c>
       <c r="D137" t="s">
         <v>59</v>
@@ -2501,7 +2501,7 @@
         <v>50</v>
       </c>
       <c r="C138">
-        <v>36.24</v>
+        <v>-36.24</v>
       </c>
       <c r="D138" t="s">
         <v>65</v>
@@ -2515,7 +2515,7 @@
         <v>47</v>
       </c>
       <c r="C139">
-        <v>92.48999999999999</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="D139" t="s">
         <v>66</v>
@@ -2529,7 +2529,7 @@
         <v>55</v>
       </c>
       <c r="C140">
-        <v>590.76</v>
+        <v>-590.76</v>
       </c>
       <c r="D140" t="s">
         <v>60</v>
@@ -2543,7 +2543,7 @@
         <v>35</v>
       </c>
       <c r="C141">
-        <v>24.56</v>
+        <v>-24.56</v>
       </c>
       <c r="D141" t="s">
         <v>59</v>
@@ -2571,7 +2571,7 @@
         <v>49</v>
       </c>
       <c r="C143">
-        <v>126.28</v>
+        <v>-126.28</v>
       </c>
       <c r="D143" t="s">
         <v>64</v>
@@ -2585,7 +2585,7 @@
         <v>39</v>
       </c>
       <c r="C144">
-        <v>123.67</v>
+        <v>-123.67</v>
       </c>
       <c r="D144" t="s">
         <v>62</v>
@@ -2599,7 +2599,7 @@
         <v>35</v>
       </c>
       <c r="C145">
-        <v>24.34</v>
+        <v>-24.34</v>
       </c>
       <c r="D145" t="s">
         <v>59</v>
@@ -2613,7 +2613,7 @@
         <v>44</v>
       </c>
       <c r="C146">
-        <v>51.46</v>
+        <v>-51.46</v>
       </c>
       <c r="D146" t="s">
         <v>66</v>
@@ -2627,7 +2627,7 @@
         <v>36</v>
       </c>
       <c r="C147">
-        <v>151.54</v>
+        <v>-151.54</v>
       </c>
       <c r="D147" t="s">
         <v>60</v>
@@ -2655,7 +2655,7 @@
         <v>40</v>
       </c>
       <c r="C149">
-        <v>118.89</v>
+        <v>-118.89</v>
       </c>
       <c r="D149" t="s">
         <v>63</v>
@@ -2669,7 +2669,7 @@
         <v>44</v>
       </c>
       <c r="C150">
-        <v>23.68</v>
+        <v>-23.68</v>
       </c>
       <c r="D150" t="s">
         <v>66</v>
@@ -2683,7 +2683,7 @@
         <v>46</v>
       </c>
       <c r="C151">
-        <v>57.48</v>
+        <v>-57.48</v>
       </c>
       <c r="D151" t="s">
         <v>59</v>
@@ -2697,7 +2697,7 @@
         <v>44</v>
       </c>
       <c r="C152">
-        <v>95.38</v>
+        <v>-95.38</v>
       </c>
       <c r="D152" t="s">
         <v>66</v>
@@ -2725,7 +2725,7 @@
         <v>39</v>
       </c>
       <c r="C154">
-        <v>126.28</v>
+        <v>-126.28</v>
       </c>
       <c r="D154" t="s">
         <v>62</v>
@@ -2739,7 +2739,7 @@
         <v>55</v>
       </c>
       <c r="C155">
-        <v>493.08</v>
+        <v>-493.08</v>
       </c>
       <c r="D155" t="s">
         <v>60</v>
@@ -2753,7 +2753,7 @@
         <v>57</v>
       </c>
       <c r="C156">
-        <v>129</v>
+        <v>-129</v>
       </c>
       <c r="D156" t="s">
         <v>63</v>
@@ -2767,7 +2767,7 @@
         <v>45</v>
       </c>
       <c r="C157">
-        <v>261.61</v>
+        <v>-261.61</v>
       </c>
       <c r="D157" t="s">
         <v>62</v>
@@ -2781,7 +2781,7 @@
         <v>55</v>
       </c>
       <c r="C158">
-        <v>617.99</v>
+        <v>-617.99</v>
       </c>
       <c r="D158" t="s">
         <v>60</v>
@@ -2795,7 +2795,7 @@
         <v>43</v>
       </c>
       <c r="C159">
-        <v>41.24</v>
+        <v>-41.24</v>
       </c>
       <c r="D159" t="s">
         <v>65</v>
@@ -2809,7 +2809,7 @@
         <v>42</v>
       </c>
       <c r="C160">
-        <v>204.93</v>
+        <v>-204.93</v>
       </c>
       <c r="D160" t="s">
         <v>64</v>
@@ -2823,7 +2823,7 @@
         <v>35</v>
       </c>
       <c r="C161">
-        <v>54.85</v>
+        <v>-54.85</v>
       </c>
       <c r="D161" t="s">
         <v>59</v>
@@ -2837,7 +2837,7 @@
         <v>58</v>
       </c>
       <c r="C162">
-        <v>17.56</v>
+        <v>-17.56</v>
       </c>
       <c r="D162" t="s">
         <v>65</v>
@@ -2851,7 +2851,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>133.02</v>
+        <v>-133.02</v>
       </c>
       <c r="D163" t="s">
         <v>66</v>
@@ -2865,7 +2865,7 @@
         <v>47</v>
       </c>
       <c r="C164">
-        <v>181.41</v>
+        <v>-181.41</v>
       </c>
       <c r="D164" t="s">
         <v>66</v>
@@ -2879,7 +2879,7 @@
         <v>45</v>
       </c>
       <c r="C165">
-        <v>484.55</v>
+        <v>-484.55</v>
       </c>
       <c r="D165" t="s">
         <v>62</v>
@@ -2893,7 +2893,7 @@
         <v>39</v>
       </c>
       <c r="C166">
-        <v>244.61</v>
+        <v>-244.61</v>
       </c>
       <c r="D166" t="s">
         <v>62</v>
@@ -2907,7 +2907,7 @@
         <v>35</v>
       </c>
       <c r="C167">
-        <v>81.06</v>
+        <v>-81.06</v>
       </c>
       <c r="D167" t="s">
         <v>59</v>
@@ -2921,7 +2921,7 @@
         <v>57</v>
       </c>
       <c r="C168">
-        <v>84.06</v>
+        <v>-84.06</v>
       </c>
       <c r="D168" t="s">
         <v>63</v>
@@ -2935,7 +2935,7 @@
         <v>56</v>
       </c>
       <c r="C169">
-        <v>43.77</v>
+        <v>-43.77</v>
       </c>
       <c r="D169" t="s">
         <v>59</v>
@@ -2949,7 +2949,7 @@
         <v>50</v>
       </c>
       <c r="C170">
-        <v>30.54</v>
+        <v>-30.54</v>
       </c>
       <c r="D170" t="s">
         <v>65</v>
@@ -2991,7 +2991,7 @@
         <v>44</v>
       </c>
       <c r="C173">
-        <v>122.88</v>
+        <v>-122.88</v>
       </c>
       <c r="D173" t="s">
         <v>66</v>
@@ -3005,7 +3005,7 @@
         <v>56</v>
       </c>
       <c r="C174">
-        <v>98.23</v>
+        <v>-98.23</v>
       </c>
       <c r="D174" t="s">
         <v>59</v>
@@ -3033,7 +3033,7 @@
         <v>49</v>
       </c>
       <c r="C176">
-        <v>185.47</v>
+        <v>-185.47</v>
       </c>
       <c r="D176" t="s">
         <v>64</v>
@@ -3047,7 +3047,7 @@
         <v>43</v>
       </c>
       <c r="C177">
-        <v>31.05</v>
+        <v>-31.05</v>
       </c>
       <c r="D177" t="s">
         <v>65</v>
@@ -3061,7 +3061,7 @@
         <v>52</v>
       </c>
       <c r="C178">
-        <v>287.46</v>
+        <v>-287.46</v>
       </c>
       <c r="D178" t="s">
         <v>64</v>
@@ -3075,7 +3075,7 @@
         <v>49</v>
       </c>
       <c r="C179">
-        <v>147.77</v>
+        <v>-147.77</v>
       </c>
       <c r="D179" t="s">
         <v>64</v>
@@ -3089,7 +3089,7 @@
         <v>41</v>
       </c>
       <c r="C180">
-        <v>155.36</v>
+        <v>-155.36</v>
       </c>
       <c r="D180" t="s">
         <v>62</v>
@@ -3103,7 +3103,7 @@
         <v>49</v>
       </c>
       <c r="C181">
-        <v>195.27</v>
+        <v>-195.27</v>
       </c>
       <c r="D181" t="s">
         <v>64</v>
@@ -3117,7 +3117,7 @@
         <v>43</v>
       </c>
       <c r="C182">
-        <v>24.82</v>
+        <v>-24.82</v>
       </c>
       <c r="D182" t="s">
         <v>65</v>
@@ -3131,7 +3131,7 @@
         <v>56</v>
       </c>
       <c r="C183">
-        <v>30.81</v>
+        <v>-30.81</v>
       </c>
       <c r="D183" t="s">
         <v>59</v>
@@ -3159,7 +3159,7 @@
         <v>54</v>
       </c>
       <c r="C185">
-        <v>101.32</v>
+        <v>-101.32</v>
       </c>
       <c r="D185" t="s">
         <v>66</v>
@@ -3173,7 +3173,7 @@
         <v>36</v>
       </c>
       <c r="C186">
-        <v>574.73</v>
+        <v>-574.73</v>
       </c>
       <c r="D186" t="s">
         <v>60</v>
@@ -3187,7 +3187,7 @@
         <v>47</v>
       </c>
       <c r="C187">
-        <v>161.86</v>
+        <v>-161.86</v>
       </c>
       <c r="D187" t="s">
         <v>66</v>
@@ -3201,7 +3201,7 @@
         <v>58</v>
       </c>
       <c r="C188">
-        <v>44.18</v>
+        <v>-44.18</v>
       </c>
       <c r="D188" t="s">
         <v>65</v>
@@ -3215,7 +3215,7 @@
         <v>35</v>
       </c>
       <c r="C189">
-        <v>51.51</v>
+        <v>-51.51</v>
       </c>
       <c r="D189" t="s">
         <v>59</v>
@@ -3229,7 +3229,7 @@
         <v>45</v>
       </c>
       <c r="C190">
-        <v>68.97</v>
+        <v>-68.97</v>
       </c>
       <c r="D190" t="s">
         <v>62</v>
@@ -3243,7 +3243,7 @@
         <v>43</v>
       </c>
       <c r="C191">
-        <v>9.380000000000001</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="D191" t="s">
         <v>65</v>
@@ -3257,7 +3257,7 @@
         <v>46</v>
       </c>
       <c r="C192">
-        <v>70.86</v>
+        <v>-70.86</v>
       </c>
       <c r="D192" t="s">
         <v>59</v>
@@ -3271,7 +3271,7 @@
         <v>45</v>
       </c>
       <c r="C193">
-        <v>319.85</v>
+        <v>-319.85</v>
       </c>
       <c r="D193" t="s">
         <v>62</v>
@@ -3285,7 +3285,7 @@
         <v>35</v>
       </c>
       <c r="C194">
-        <v>70.97</v>
+        <v>-70.97</v>
       </c>
       <c r="D194" t="s">
         <v>59</v>
@@ -3299,7 +3299,7 @@
         <v>42</v>
       </c>
       <c r="C195">
-        <v>31.11</v>
+        <v>-31.11</v>
       </c>
       <c r="D195" t="s">
         <v>64</v>
@@ -3327,7 +3327,7 @@
         <v>50</v>
       </c>
       <c r="C197">
-        <v>18.5</v>
+        <v>-18.5</v>
       </c>
       <c r="D197" t="s">
         <v>65</v>
@@ -3355,7 +3355,7 @@
         <v>36</v>
       </c>
       <c r="C199">
-        <v>890.04</v>
+        <v>-890.04</v>
       </c>
       <c r="D199" t="s">
         <v>60</v>
@@ -3369,7 +3369,7 @@
         <v>55</v>
       </c>
       <c r="C200">
-        <v>646.27</v>
+        <v>-646.27</v>
       </c>
       <c r="D200" t="s">
         <v>60</v>
@@ -3383,7 +3383,7 @@
         <v>35</v>
       </c>
       <c r="C201">
-        <v>20.87</v>
+        <v>-20.87</v>
       </c>
       <c r="D201" t="s">
         <v>59</v>
